--- a/sheet/SpellCardData.xlsx
+++ b/sheet/SpellCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796506C3-E9FE-43C4-91D1-D2C59E57C882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF77EB9-CCBC-4774-AAAD-A91C971E538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,10 +200,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对手牌中1张怪物牌使用：消灭那张牌，然后获得遭遇牌堆第1张道具牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>失能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -218,6 +214,10 @@
   <si>
     <t>①对遭遇牌弃牌堆使用：选1张牌放在遭遇牌堆顶。&lt;br&gt;
 ②对弃牌堆使用：选1张牌放在主牌堆顶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对受玩家控制的1张怪物牌使用：消灭那张牌，然后获得遭遇牌堆第1张道具牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -780,24 +780,24 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="171" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SpellCardData.xlsx
+++ b/sheet/SpellCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF77EB9-CCBC-4774-AAAD-A91C971E538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7294A694-D783-4544-95F3-89E1B6676A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对道具牌区中的1张《未知卷轴》牌使用：弃置那张牌，然后从法术牌堆抽3张牌，选其中1张加入法术表。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>驱散</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,10 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上1张怪物牌使用：消灭那张怪物牌，然后获得与被消灭的怪物牌点数相同的金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>援军</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,14 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对1个房间的一侧使用：那一侧所有牌点数加1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对1个房间的一侧使用：那一侧所有牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>传送</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,10 +151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上1张怪物牌使用：将那张牌移动到对侧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>献祭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,15 +168,6 @@
   </si>
   <si>
     <t>放逐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对场上1张化身牌使用：将至多4张点数为1的化身牌放入与目标牌相邻的房间的任意一侧，每个房间至多1张。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>①未叠放其他牌时，对场上1张牌使用：将那张牌叠放在本牌下方。&lt;br&gt;
-②叠放了其他牌时，对1个房间的一侧使用：将叠放的牌移动到那里。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -218,6 +189,35 @@
   </si>
   <si>
     <t>对受玩家控制的1张怪物牌使用：消灭那张牌，然后获得遭遇牌堆第1张道具牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对场上1张化身牌使用：将至多4张点数为1的化身牌放入与目标牌相邻的房间，阵营自由，每个房间至多1张。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对1个房间的1个阵营使用：该阵营所有牌点数加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对1个房间的1个阵营使用：该阵营所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对场上1张怪物牌使用：改变那张牌的阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①未叠放其他牌时，对场上1张牌使用：将那张牌叠放在本牌下方。&lt;br&gt;
+②叠放了其他牌时，对1个房间使用：将叠放的牌移动到那个房间，阵营自由。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对场上1张怪物牌使用：消灭那张怪物牌，然后获得遭遇牌堆第一张《金块》。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对背包区中的1张《未知卷轴》牌使用：弃置那张牌，然后从升级牌堆翻开第1张法术牌，将其加入法术表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -632,117 +632,117 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>18</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -753,51 +753,51 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="256.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="171" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SpellCardData.xlsx
+++ b/sheet/SpellCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7294A694-D783-4544-95F3-89E1B6676A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA8045A-0C85-4C85-8FE0-55F4E91D3762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对1个牌堆使用：观看其顶端5张牌，将其中任意张牌以任意顺序放在牌堆顶部，其余牌按任意顺序放在牌堆底部。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对场上或手牌中1张怪物牌使用：重抽那张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -107,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宣言1个种族：消灭场上和手牌中所有标签中带有那个种族的怪物牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>点金</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,10 +168,6 @@
   </si>
   <si>
     <t>对场上1张牌使用：横置那张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回响</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -218,6 +206,18 @@
   </si>
   <si>
     <t>对背包区中的1张《未知卷轴》牌使用：弃置那张牌，然后从升级牌堆翻开第1张法术牌，将其加入法术表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对手牌中的1张怪物牌使用：消灭那张怪物牌，然后消灭场上所有种族与其有交集的怪物牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对1个牌堆使用：将持有的1张属于那个牌堆的牌洗回那个牌堆，然后观看其顶端5张牌，将其中任意张牌以任意顺序放在牌堆顶部，其余牌按任意顺序放在牌堆底部。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回溯</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -585,10 +585,10 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -596,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -607,10 +607,10 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -621,128 +621,128 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -753,51 +753,51 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="256.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="171" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SpellCardData.xlsx
+++ b/sheet/SpellCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA8045A-0C85-4C85-8FE0-55F4E91D3762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6AA18F-BB98-4DB6-A462-7DD963D137A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,14 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>镜像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对场上1张怪物牌使用：从主牌堆将1张其同名牌加入手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>预言</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,22 +75,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上或手牌中1张怪物牌使用：重抽那张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鉴定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>驱散</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消灭场上所有“杂鱼”牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>灭绝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上1张陷阱牌使用：将那张牌加入手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>祝福</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上1张牌使用：将那张牌移动到另一个房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>混乱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,57 +139,69 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对场上1张牌使用：横置那张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>①对遭遇牌弃牌堆使用：选1张牌放在遭遇牌堆顶。&lt;br&gt;
-②对弃牌堆使用：选1张牌放在主牌堆顶。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对受玩家控制的1张怪物牌使用：消灭那张牌，然后获得遭遇牌堆第1张道具牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对场上1张化身牌使用：将至多4张点数为1的化身牌放入与目标牌相邻的房间，阵营自由，每个房间至多1张。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对1个房间的1个阵营使用：该阵营所有牌点数加1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对1个房间的1个阵营使用：该阵营所有牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对场上1张怪物牌使用：改变那张牌的阵营。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>①未叠放其他牌时，对场上1张牌使用：将那张牌叠放在本牌下方。&lt;br&gt;
-②叠放了其他牌时，对1个房间使用：将叠放的牌移动到那个房间，阵营自由。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对场上1张怪物牌使用：消灭那张怪物牌，然后获得遭遇牌堆第一张《金块》。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对背包区中的1张《未知卷轴》牌使用：弃置那张牌，然后从升级牌堆翻开第1张法术牌，将其加入法术表。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对手牌中的1张怪物牌使用：消灭那张怪物牌，然后消灭场上所有种族与其有交集的怪物牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对1个牌堆使用：将持有的1张属于那个牌堆的牌洗回那个牌堆，然后观看其顶端5张牌，将其中任意张牌以任意顺序放在牌堆顶部，其余牌按任意顺序放在牌堆底部。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>回溯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消灭楼层区所有“杂鱼”牌。</t>
+  </si>
+  <si>
+    <t>对手牌中的1张怪物牌使用：消灭那张怪物牌，然后消灭楼层区所有种族与其有交集的怪物牌。</t>
+  </si>
+  <si>
+    <t>对楼层区1张陷阱牌使用：将那张牌加入手牌。</t>
+  </si>
+  <si>
+    <t>对楼层区1张牌使用：将那张牌移动到另一个房间。</t>
+  </si>
+  <si>
+    <t>对楼层区1张怪物牌使用：改变那张牌的阵营。</t>
+  </si>
+  <si>
+    <t>对楼层区1张牌使用：横置那张牌。</t>
+  </si>
+  <si>
+    <t>对楼层区1张怪物牌使用：从主牌堆将1张其同名牌加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对楼层区或手牌中1张怪物牌使用：重抽那张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对楼层区1张怪物牌使用：消灭那张怪物牌，然后获得1金币或获得遭遇牌堆第一张《金块》。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对1个房间的一侧使用：该侧所有牌点数加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对1个房间的一侧使用：该侧所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活体炸弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对楼层区1张受玩家控制的怪物牌使用：消灭那张牌，然后同房间所有其他牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对受玩家控制的1张怪物牌使用：消灭那张牌，然后从遭遇牌堆翻开3张牌，获得其中的1张道具牌或弹药牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将楼层区1张牌洗回主牌堆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对任意弃牌堆使用：将该牌堆顶端顶端的1张牌洗回其来源牌堆。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -582,24 +566,24 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -607,197 +591,186 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="256.5" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="114" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="171" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>36</v>
+      <c r="C21" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SpellCardData.xlsx
+++ b/sheet/SpellCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6AA18F-BB98-4DB6-A462-7DD963D137A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E261AE4-EFCA-4D26-8146-9E85F1E75C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>传送</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>混乱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,9 +152,6 @@
     <t>对楼层区1张陷阱牌使用：将那张牌加入手牌。</t>
   </si>
   <si>
-    <t>对楼层区1张牌使用：将那张牌移动到另一个房间。</t>
-  </si>
-  <si>
     <t>对楼层区1张怪物牌使用：改变那张牌的阵营。</t>
   </si>
   <si>
@@ -202,6 +195,14 @@
   </si>
   <si>
     <t>对任意弃牌堆使用：将该牌堆顶端顶端的1张牌洗回其来源牌堆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对楼层区2张牌使用：交换那两张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -583,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -594,7 +595,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -605,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -616,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -627,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -649,7 +650,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -660,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -671,51 +672,51 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -726,51 +727,51 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="114" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
